--- a/output/upload/S00026_2246_H건강플러스보험_무배당.xlsx
+++ b/output/upload/S00026_2246_H건강플러스보험_무배당.xlsx
@@ -1304,17 +1304,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -1398,17 +1390,9 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
@@ -1492,17 +1476,9 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
@@ -1586,17 +1562,9 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="6" t="inlineStr">
@@ -1680,17 +1648,9 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="inlineStr">
@@ -1774,17 +1734,9 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
@@ -1868,17 +1820,9 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="inlineStr">
@@ -1962,17 +1906,9 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="6" t="inlineStr">
@@ -2056,17 +1992,9 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="6" t="inlineStr">
@@ -2150,17 +2078,9 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="6" t="inlineStr">
@@ -2244,17 +2164,9 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="6" t="inlineStr">
@@ -2338,17 +2250,9 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
+      <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="6" t="inlineStr">
@@ -2432,17 +2336,9 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
+      <c r="B19" s="5" t="inlineStr"/>
       <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="6" t="inlineStr">
@@ -2526,17 +2422,9 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
+      <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="6" t="inlineStr">
@@ -2620,17 +2508,9 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="6" t="inlineStr">
@@ -2714,17 +2594,9 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="6" t="inlineStr">
@@ -2807,16 +2679,8 @@
       <c r="AV22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2867,16 +2731,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2927,16 +2783,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2987,16 +2835,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3047,16 +2887,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3107,16 +2939,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3167,16 +2991,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3227,16 +3043,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3287,16 +3095,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3347,16 +3147,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3407,16 +3199,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3467,16 +3251,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3527,16 +3303,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3587,16 +3355,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3647,16 +3407,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3707,16 +3459,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3767,16 +3511,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3827,16 +3563,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3887,16 +3615,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3947,16 +3667,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4007,16 +3719,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4067,16 +3771,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4127,16 +3823,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4187,16 +3875,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4247,16 +3927,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4307,16 +3979,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4367,16 +4031,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4427,16 +4083,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4487,16 +4135,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4547,16 +4187,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4607,16 +4239,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4667,16 +4291,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4727,16 +4343,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4787,16 +4395,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4847,16 +4447,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4907,16 +4499,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4967,16 +4551,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5027,16 +4603,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5087,16 +4655,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5147,16 +4707,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5207,16 +4759,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5267,16 +4811,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5327,16 +4863,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5387,16 +4915,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5447,16 +4967,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5507,16 +5019,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5567,16 +5071,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5627,16 +5123,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5687,16 +5175,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5747,16 +5227,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5807,16 +5279,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5867,16 +5331,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5927,16 +5383,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5987,16 +5435,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6047,16 +5487,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6107,16 +5539,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6167,16 +5591,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6227,16 +5643,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6287,16 +5695,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6347,16 +5747,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6407,16 +5799,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6467,16 +5851,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6527,16 +5903,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6587,16 +5955,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6647,16 +6007,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6707,16 +6059,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6767,16 +6111,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6827,16 +6163,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6887,16 +6215,8 @@
       </c>
     </row>
     <row r="91">
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6947,16 +6267,8 @@
       </c>
     </row>
     <row r="92">
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7007,16 +6319,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7067,16 +6371,8 @@
       </c>
     </row>
     <row r="94">
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7127,16 +6423,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7187,16 +6475,8 @@
       </c>
     </row>
     <row r="96">
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7247,16 +6527,8 @@
       </c>
     </row>
     <row r="97">
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7307,16 +6579,8 @@
       </c>
     </row>
     <row r="98">
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7367,16 +6631,8 @@
       </c>
     </row>
     <row r="99">
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7427,16 +6683,8 @@
       </c>
     </row>
     <row r="100">
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7487,16 +6735,8 @@
       </c>
     </row>
     <row r="101">
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7547,16 +6787,8 @@
       </c>
     </row>
     <row r="102">
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7607,16 +6839,8 @@
       </c>
     </row>
     <row r="103">
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7667,16 +6891,8 @@
       </c>
     </row>
     <row r="104">
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7727,16 +6943,8 @@
       </c>
     </row>
     <row r="105">
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7787,16 +6995,8 @@
       </c>
     </row>
     <row r="106">
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7847,16 +7047,8 @@
       </c>
     </row>
     <row r="107">
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7907,16 +7099,8 @@
       </c>
     </row>
     <row r="108">
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7967,16 +7151,8 @@
       </c>
     </row>
     <row r="109">
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8027,16 +7203,8 @@
       </c>
     </row>
     <row r="110">
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8087,16 +7255,8 @@
       </c>
     </row>
     <row r="111">
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8147,16 +7307,8 @@
       </c>
     </row>
     <row r="112">
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8207,16 +7359,8 @@
       </c>
     </row>
     <row r="113">
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8267,16 +7411,8 @@
       </c>
     </row>
     <row r="114">
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8327,16 +7463,8 @@
       </c>
     </row>
     <row r="115">
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8387,16 +7515,8 @@
       </c>
     </row>
     <row r="116">
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8447,16 +7567,8 @@
       </c>
     </row>
     <row r="117">
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8507,16 +7619,8 @@
       </c>
     </row>
     <row r="118">
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8567,16 +7671,8 @@
       </c>
     </row>
     <row r="119">
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8627,16 +7723,8 @@
       </c>
     </row>
     <row r="120">
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8687,16 +7775,8 @@
       </c>
     </row>
     <row r="121">
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8747,16 +7827,8 @@
       </c>
     </row>
     <row r="122">
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8807,16 +7879,8 @@
       </c>
     </row>
     <row r="123">
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8867,16 +7931,8 @@
       </c>
     </row>
     <row r="124">
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8927,16 +7983,8 @@
       </c>
     </row>
     <row r="125">
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8987,16 +8035,8 @@
       </c>
     </row>
     <row r="126">
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9047,16 +8087,8 @@
       </c>
     </row>
     <row r="127">
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9107,16 +8139,8 @@
       </c>
     </row>
     <row r="128">
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9167,16 +8191,8 @@
       </c>
     </row>
     <row r="129">
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9227,16 +8243,8 @@
       </c>
     </row>
     <row r="130">
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9287,16 +8295,8 @@
       </c>
     </row>
     <row r="131">
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9347,16 +8347,8 @@
       </c>
     </row>
     <row r="132">
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9407,16 +8399,8 @@
       </c>
     </row>
     <row r="133">
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9467,16 +8451,8 @@
       </c>
     </row>
     <row r="134">
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9527,16 +8503,8 @@
       </c>
     </row>
     <row r="135">
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9587,16 +8555,8 @@
       </c>
     </row>
     <row r="136">
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9647,16 +8607,8 @@
       </c>
     </row>
     <row r="137">
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9707,16 +8659,8 @@
       </c>
     </row>
     <row r="138">
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9767,16 +8711,8 @@
       </c>
     </row>
     <row r="139">
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9827,16 +8763,8 @@
       </c>
     </row>
     <row r="140">
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9887,16 +8815,8 @@
       </c>
     </row>
     <row r="141">
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9947,16 +8867,8 @@
       </c>
     </row>
     <row r="142">
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10007,16 +8919,8 @@
       </c>
     </row>
     <row r="143">
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10067,16 +8971,8 @@
       </c>
     </row>
     <row r="144">
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10127,16 +9023,8 @@
       </c>
     </row>
     <row r="145">
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10187,16 +9075,8 @@
       </c>
     </row>
     <row r="146">
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10247,16 +9127,8 @@
       </c>
     </row>
     <row r="147">
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10307,16 +9179,8 @@
       </c>
     </row>
     <row r="148">
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10367,16 +9231,8 @@
       </c>
     </row>
     <row r="149">
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10427,16 +9283,8 @@
       </c>
     </row>
     <row r="150">
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10487,16 +9335,8 @@
       </c>
     </row>
     <row r="151">
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10547,16 +9387,8 @@
       </c>
     </row>
     <row r="152">
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10607,16 +9439,8 @@
       </c>
     </row>
     <row r="153">
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10667,16 +9491,8 @@
       </c>
     </row>
     <row r="154">
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10727,16 +9543,8 @@
       </c>
     </row>
     <row r="155">
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10787,16 +9595,8 @@
       </c>
     </row>
     <row r="156">
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10847,16 +9647,8 @@
       </c>
     </row>
     <row r="157">
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10907,16 +9699,8 @@
       </c>
     </row>
     <row r="158">
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10967,16 +9751,8 @@
       </c>
     </row>
     <row r="159">
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -11027,16 +9803,8 @@
       </c>
     </row>
     <row r="160">
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -11087,16 +9855,8 @@
       </c>
     </row>
     <row r="161">
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -11147,16 +9907,8 @@
       </c>
     </row>
     <row r="162">
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -11207,16 +9959,8 @@
       </c>
     </row>
     <row r="163">
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -11267,16 +10011,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -11327,16 +10063,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -11387,16 +10115,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -11447,16 +10167,8 @@
       </c>
     </row>
     <row r="167">
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -11507,16 +10219,8 @@
       </c>
     </row>
     <row r="168">
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
           <t>20260201</t>

--- a/output/upload/S00026_2246_H건강플러스보험_무배당.xlsx
+++ b/output/upload/S00026_2246_H건강플러스보험_무배당.xlsx
@@ -1304,11 +1304,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1390,11 +1410,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1476,11 +1516,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1562,11 +1622,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1648,11 +1728,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1734,11 +1834,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1820,11 +1940,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1906,11 +2046,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1992,11 +2152,31 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2078,11 +2258,31 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2164,11 +2364,31 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2250,11 +2470,31 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2336,11 +2576,31 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2422,11 +2682,31 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2508,11 +2788,31 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2594,11 +2894,31 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2679,8 +2999,31 @@
       <c r="AV22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2731,8 +3074,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2783,8 +3149,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2835,8 +3224,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2887,8 +3299,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2939,8 +3374,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2991,8 +3449,31 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3043,8 +3524,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3095,8 +3599,31 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3147,8 +3674,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3199,8 +3749,31 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3251,8 +3824,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3303,8 +3899,31 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3355,8 +3974,31 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3407,8 +4049,31 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3459,8 +4124,31 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3511,8 +4199,31 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3563,8 +4274,31 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3615,8 +4349,31 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3667,8 +4424,31 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3719,8 +4499,31 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3771,8 +4574,31 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3823,8 +4649,31 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3875,8 +4724,31 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3927,8 +4799,31 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3979,8 +4874,31 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4031,8 +4949,31 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4083,8 +5024,31 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4135,8 +5099,31 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4187,8 +5174,31 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4239,8 +5249,31 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4291,8 +5324,31 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4343,8 +5399,31 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4395,8 +5474,31 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4447,8 +5549,31 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4499,8 +5624,31 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4551,8 +5699,31 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4603,8 +5774,31 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4655,8 +5849,31 @@
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4707,8 +5924,31 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4759,8 +5999,31 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4811,8 +6074,31 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4863,8 +6149,31 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4915,8 +6224,31 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4967,8 +6299,31 @@
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5019,8 +6374,31 @@
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5071,8 +6449,31 @@
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5123,8 +6524,31 @@
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5175,8 +6599,31 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5227,8 +6674,31 @@
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5279,8 +6749,31 @@
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5331,8 +6824,31 @@
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5383,8 +6899,31 @@
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5435,8 +6974,31 @@
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5487,8 +7049,31 @@
       </c>
     </row>
     <row r="77">
-      <c r="B77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5539,8 +7124,31 @@
       </c>
     </row>
     <row r="78">
-      <c r="B78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5591,8 +7199,31 @@
       </c>
     </row>
     <row r="79">
-      <c r="B79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5643,8 +7274,31 @@
       </c>
     </row>
     <row r="80">
-      <c r="B80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5695,8 +7349,31 @@
       </c>
     </row>
     <row r="81">
-      <c r="B81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5747,8 +7424,31 @@
       </c>
     </row>
     <row r="82">
-      <c r="B82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5799,8 +7499,31 @@
       </c>
     </row>
     <row r="83">
-      <c r="B83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5851,8 +7574,31 @@
       </c>
     </row>
     <row r="84">
-      <c r="B84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5903,8 +7649,31 @@
       </c>
     </row>
     <row r="85">
-      <c r="B85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5955,8 +7724,31 @@
       </c>
     </row>
     <row r="86">
-      <c r="B86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6007,8 +7799,31 @@
       </c>
     </row>
     <row r="87">
-      <c r="B87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6059,8 +7874,31 @@
       </c>
     </row>
     <row r="88">
-      <c r="B88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6111,8 +7949,31 @@
       </c>
     </row>
     <row r="89">
-      <c r="B89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6163,8 +8024,31 @@
       </c>
     </row>
     <row r="90">
-      <c r="B90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6215,8 +8099,31 @@
       </c>
     </row>
     <row r="91">
-      <c r="B91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6267,8 +8174,31 @@
       </c>
     </row>
     <row r="92">
-      <c r="B92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6319,8 +8249,31 @@
       </c>
     </row>
     <row r="93">
-      <c r="B93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6371,8 +8324,31 @@
       </c>
     </row>
     <row r="94">
-      <c r="B94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6423,8 +8399,31 @@
       </c>
     </row>
     <row r="95">
-      <c r="B95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6475,8 +8474,31 @@
       </c>
     </row>
     <row r="96">
-      <c r="B96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6527,8 +8549,31 @@
       </c>
     </row>
     <row r="97">
-      <c r="B97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6579,8 +8624,31 @@
       </c>
     </row>
     <row r="98">
-      <c r="B98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6631,8 +8699,31 @@
       </c>
     </row>
     <row r="99">
-      <c r="B99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6683,8 +8774,31 @@
       </c>
     </row>
     <row r="100">
-      <c r="B100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6735,8 +8849,31 @@
       </c>
     </row>
     <row r="101">
-      <c r="B101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6787,8 +8924,31 @@
       </c>
     </row>
     <row r="102">
-      <c r="B102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6839,8 +8999,31 @@
       </c>
     </row>
     <row r="103">
-      <c r="B103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6891,8 +9074,31 @@
       </c>
     </row>
     <row r="104">
-      <c r="B104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6943,8 +9149,31 @@
       </c>
     </row>
     <row r="105">
-      <c r="B105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6995,8 +9224,31 @@
       </c>
     </row>
     <row r="106">
-      <c r="B106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7047,8 +9299,31 @@
       </c>
     </row>
     <row r="107">
-      <c r="B107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7099,8 +9374,31 @@
       </c>
     </row>
     <row r="108">
-      <c r="B108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7151,8 +9449,31 @@
       </c>
     </row>
     <row r="109">
-      <c r="B109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7203,8 +9524,31 @@
       </c>
     </row>
     <row r="110">
-      <c r="B110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7255,8 +9599,31 @@
       </c>
     </row>
     <row r="111">
-      <c r="B111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7307,8 +9674,31 @@
       </c>
     </row>
     <row r="112">
-      <c r="B112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G112" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7359,8 +9749,31 @@
       </c>
     </row>
     <row r="113">
-      <c r="B113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7411,8 +9824,31 @@
       </c>
     </row>
     <row r="114">
-      <c r="B114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7463,8 +9899,31 @@
       </c>
     </row>
     <row r="115">
-      <c r="B115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7515,8 +9974,31 @@
       </c>
     </row>
     <row r="116">
-      <c r="B116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7567,8 +10049,31 @@
       </c>
     </row>
     <row r="117">
-      <c r="B117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7619,8 +10124,31 @@
       </c>
     </row>
     <row r="118">
-      <c r="B118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7671,8 +10199,31 @@
       </c>
     </row>
     <row r="119">
-      <c r="B119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7723,8 +10274,31 @@
       </c>
     </row>
     <row r="120">
-      <c r="B120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7775,8 +10349,31 @@
       </c>
     </row>
     <row r="121">
-      <c r="B121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7827,8 +10424,31 @@
       </c>
     </row>
     <row r="122">
-      <c r="B122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7879,8 +10499,31 @@
       </c>
     </row>
     <row r="123">
-      <c r="B123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7931,8 +10574,31 @@
       </c>
     </row>
     <row r="124">
-      <c r="B124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G124" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -7983,8 +10649,31 @@
       </c>
     </row>
     <row r="125">
-      <c r="B125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8035,8 +10724,31 @@
       </c>
     </row>
     <row r="126">
-      <c r="B126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G126" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8087,8 +10799,31 @@
       </c>
     </row>
     <row r="127">
-      <c r="B127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8139,8 +10874,31 @@
       </c>
     </row>
     <row r="128">
-      <c r="B128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8191,8 +10949,31 @@
       </c>
     </row>
     <row r="129">
-      <c r="B129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8243,8 +11024,31 @@
       </c>
     </row>
     <row r="130">
-      <c r="B130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G130" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8295,8 +11099,31 @@
       </c>
     </row>
     <row r="131">
-      <c r="B131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G131" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8347,8 +11174,31 @@
       </c>
     </row>
     <row r="132">
-      <c r="B132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8399,8 +11249,31 @@
       </c>
     </row>
     <row r="133">
-      <c r="B133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8451,8 +11324,31 @@
       </c>
     </row>
     <row r="134">
-      <c r="B134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G134" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8503,8 +11399,31 @@
       </c>
     </row>
     <row r="135">
-      <c r="B135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8555,8 +11474,31 @@
       </c>
     </row>
     <row r="136">
-      <c r="B136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8607,8 +11549,31 @@
       </c>
     </row>
     <row r="137">
-      <c r="B137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G137" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8659,8 +11624,31 @@
       </c>
     </row>
     <row r="138">
-      <c r="B138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G138" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8711,8 +11699,31 @@
       </c>
     </row>
     <row r="139">
-      <c r="B139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G139" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8763,8 +11774,31 @@
       </c>
     </row>
     <row r="140">
-      <c r="B140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G140" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8815,8 +11849,31 @@
       </c>
     </row>
     <row r="141">
-      <c r="B141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G141" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8867,8 +11924,31 @@
       </c>
     </row>
     <row r="142">
-      <c r="B142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G142" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8919,8 +11999,31 @@
       </c>
     </row>
     <row r="143">
-      <c r="B143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G143" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -8971,8 +12074,31 @@
       </c>
     </row>
     <row r="144">
-      <c r="B144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G144" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9023,8 +12149,31 @@
       </c>
     </row>
     <row r="145">
-      <c r="B145" t="inlineStr"/>
-      <c r="D145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G145" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9075,8 +12224,31 @@
       </c>
     </row>
     <row r="146">
-      <c r="B146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G146" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9127,8 +12299,31 @@
       </c>
     </row>
     <row r="147">
-      <c r="B147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G147" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9179,8 +12374,31 @@
       </c>
     </row>
     <row r="148">
-      <c r="B148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G148" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9231,8 +12449,31 @@
       </c>
     </row>
     <row r="149">
-      <c r="B149" t="inlineStr"/>
-      <c r="D149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G149" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9283,8 +12524,31 @@
       </c>
     </row>
     <row r="150">
-      <c r="B150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G150" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9335,8 +12599,31 @@
       </c>
     </row>
     <row r="151">
-      <c r="B151" t="inlineStr"/>
-      <c r="D151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G151" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9387,8 +12674,31 @@
       </c>
     </row>
     <row r="152">
-      <c r="B152" t="inlineStr"/>
-      <c r="D152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G152" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9439,8 +12749,31 @@
       </c>
     </row>
     <row r="153">
-      <c r="B153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G153" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9491,8 +12824,31 @@
       </c>
     </row>
     <row r="154">
-      <c r="B154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G154" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9543,8 +12899,31 @@
       </c>
     </row>
     <row r="155">
-      <c r="B155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G155" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9595,8 +12974,31 @@
       </c>
     </row>
     <row r="156">
-      <c r="B156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G156" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9647,8 +13049,31 @@
       </c>
     </row>
     <row r="157">
-      <c r="B157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G157" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9699,8 +13124,31 @@
       </c>
     </row>
     <row r="158">
-      <c r="B158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G158" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9751,8 +13199,31 @@
       </c>
     </row>
     <row r="159">
-      <c r="B159" t="inlineStr"/>
-      <c r="D159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G159" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9803,8 +13274,31 @@
       </c>
     </row>
     <row r="160">
-      <c r="B160" t="inlineStr"/>
-      <c r="D160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G160" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9855,8 +13349,31 @@
       </c>
     </row>
     <row r="161">
-      <c r="B161" t="inlineStr"/>
-      <c r="D161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G161" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9907,8 +13424,31 @@
       </c>
     </row>
     <row r="162">
-      <c r="B162" t="inlineStr"/>
-      <c r="D162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G162" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -9959,8 +13499,31 @@
       </c>
     </row>
     <row r="163">
-      <c r="B163" t="inlineStr"/>
-      <c r="D163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G163" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10011,8 +13574,31 @@
       </c>
     </row>
     <row r="164">
-      <c r="B164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G164" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10063,8 +13649,31 @@
       </c>
     </row>
     <row r="165">
-      <c r="B165" t="inlineStr"/>
-      <c r="D165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G165" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10115,8 +13724,31 @@
       </c>
     </row>
     <row r="166">
-      <c r="B166" t="inlineStr"/>
-      <c r="D166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G166" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10167,8 +13799,31 @@
       </c>
     </row>
     <row r="167">
-      <c r="B167" t="inlineStr"/>
-      <c r="D167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G167" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -10219,8 +13874,31 @@
       </c>
     </row>
     <row r="168">
-      <c r="B168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr">
         <is>
           <t>20260201</t>

--- a/output/upload/S00026_2246_H건강플러스보험_무배당.xlsx
+++ b/output/upload/S00026_2246_H건강플러스보험_무배당.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11186,7 +11186,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11261,7 +11261,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -11636,7 +11636,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -13511,7 +13511,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -13661,7 +13661,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">

--- a/output/upload/S00026_2246_H건강플러스보험_무배당.xlsx
+++ b/output/upload/S00026_2246_H건강플러스보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV168"/>
+  <dimension ref="A1:AV177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P25" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="X25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3226,22 +3226,22 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3294,29 +3294,29 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3338,7 +3338,7 @@
         <v>15</v>
       </c>
       <c r="K27" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P27" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3369,29 +3369,29 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3444,29 +3444,29 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P29" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -3519,29 +3519,29 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3594,29 +3594,29 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3638,7 +3638,7 @@
         <v>15</v>
       </c>
       <c r="K31" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P31" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="X31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -3669,29 +3669,29 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3744,29 +3744,29 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3788,7 +3788,7 @@
         <v>15</v>
       </c>
       <c r="K33" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P33" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -3819,29 +3819,29 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3894,29 +3894,29 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P35" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -3969,29 +3969,29 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4044,29 +4044,29 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4088,7 +4088,7 @@
         <v>15</v>
       </c>
       <c r="K37" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -4096,10 +4096,10 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P37" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="X37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -4119,29 +4119,29 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4194,29 +4194,29 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4238,7 +4238,7 @@
         <v>15</v>
       </c>
       <c r="K39" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P39" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -4269,29 +4269,29 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4344,29 +4344,29 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4388,7 +4388,7 @@
         <v>15</v>
       </c>
       <c r="K41" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -4419,29 +4419,29 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4494,29 +4494,29 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4538,7 +4538,7 @@
         <v>15</v>
       </c>
       <c r="K43" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P43" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="X43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -4569,29 +4569,29 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P44" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="X44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -4644,29 +4644,29 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4688,7 +4688,7 @@
         <v>15</v>
       </c>
       <c r="K45" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P45" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -4726,22 +4726,22 @@
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4763,7 +4763,7 @@
         <v>15</v>
       </c>
       <c r="K46" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -4771,10 +4771,10 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P46" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -4801,22 +4801,22 @@
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -4876,22 +4876,22 @@
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P48" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -4951,22 +4951,22 @@
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4988,7 +4988,7 @@
         <v>15</v>
       </c>
       <c r="K49" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P49" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="X49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
@@ -5026,22 +5026,22 @@
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5063,7 +5063,7 @@
         <v>15</v>
       </c>
       <c r="K50" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P50" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="X50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
@@ -5101,22 +5101,22 @@
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5138,7 +5138,7 @@
         <v>15</v>
       </c>
       <c r="K51" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P51" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -5176,22 +5176,22 @@
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5213,7 +5213,7 @@
         <v>15</v>
       </c>
       <c r="K52" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P52" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -5251,22 +5251,22 @@
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P53" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -5326,22 +5326,22 @@
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P54" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -5401,22 +5401,22 @@
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5438,7 +5438,7 @@
         <v>15</v>
       </c>
       <c r="K55" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -5446,10 +5446,10 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P55" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="X55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
@@ -5476,22 +5476,22 @@
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5513,7 +5513,7 @@
         <v>15</v>
       </c>
       <c r="K56" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P56" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="X56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
@@ -5551,22 +5551,22 @@
     <row r="57">
       <c r="B57" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5588,7 +5588,7 @@
         <v>15</v>
       </c>
       <c r="K57" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -5596,10 +5596,10 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P57" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -5626,22 +5626,22 @@
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5663,7 +5663,7 @@
         <v>15</v>
       </c>
       <c r="K58" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P58" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -5701,22 +5701,22 @@
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5738,7 +5738,7 @@
         <v>15</v>
       </c>
       <c r="K59" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P59" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -5776,22 +5776,22 @@
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5813,7 +5813,7 @@
         <v>15</v>
       </c>
       <c r="K60" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P60" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -5851,22 +5851,22 @@
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5888,7 +5888,7 @@
         <v>15</v>
       </c>
       <c r="K61" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P61" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -5907,10 +5907,10 @@
         </is>
       </c>
       <c r="X61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
@@ -5926,22 +5926,22 @@
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5963,7 +5963,7 @@
         <v>15</v>
       </c>
       <c r="K62" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -5971,10 +5971,10 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P62" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -5982,10 +5982,10 @@
         </is>
       </c>
       <c r="X62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
@@ -6001,22 +6001,22 @@
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6038,7 +6038,7 @@
         <v>15</v>
       </c>
       <c r="K63" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="X63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
@@ -6076,22 +6076,22 @@
     <row r="64">
       <c r="B64" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6113,7 +6113,7 @@
         <v>15</v>
       </c>
       <c r="K64" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P64" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -6144,29 +6144,29 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6188,7 +6188,7 @@
         <v>15</v>
       </c>
       <c r="K65" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -6196,10 +6196,10 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P65" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -6219,29 +6219,29 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6271,10 +6271,10 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P66" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -6294,29 +6294,29 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6338,7 +6338,7 @@
         <v>15</v>
       </c>
       <c r="K67" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -6346,10 +6346,10 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P67" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="X67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
@@ -6369,29 +6369,29 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6413,7 +6413,7 @@
         <v>15</v>
       </c>
       <c r="K68" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -6421,10 +6421,10 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P68" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="X68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
@@ -6444,29 +6444,29 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P69" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -6507,10 +6507,10 @@
         </is>
       </c>
       <c r="X69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
@@ -6519,29 +6519,29 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6563,7 +6563,7 @@
         <v>15</v>
       </c>
       <c r="K70" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -6571,10 +6571,10 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P70" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -6594,29 +6594,29 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6638,7 +6638,7 @@
         <v>15</v>
       </c>
       <c r="K71" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P71" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -6669,29 +6669,29 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6721,10 +6721,10 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P72" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -6744,29 +6744,29 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6788,7 +6788,7 @@
         <v>15</v>
       </c>
       <c r="K73" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -6796,10 +6796,10 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P73" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -6807,10 +6807,10 @@
         </is>
       </c>
       <c r="X73" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y73" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
@@ -6819,29 +6819,29 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6863,7 +6863,7 @@
         <v>15</v>
       </c>
       <c r="K74" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P74" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -6882,10 +6882,10 @@
         </is>
       </c>
       <c r="X74" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y74" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
@@ -6894,29 +6894,29 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6938,7 +6938,7 @@
         <v>15</v>
       </c>
       <c r="K75" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -6946,10 +6946,10 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P75" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -6957,10 +6957,10 @@
         </is>
       </c>
       <c r="X75" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y75" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
@@ -6969,29 +6969,29 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7013,7 +7013,7 @@
         <v>15</v>
       </c>
       <c r="K76" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P76" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -7044,29 +7044,29 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -7088,7 +7088,7 @@
         <v>15</v>
       </c>
       <c r="K77" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P77" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -7119,29 +7119,29 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -7163,7 +7163,7 @@
         <v>15</v>
       </c>
       <c r="K78" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P78" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -7194,29 +7194,29 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -7246,10 +7246,10 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P79" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="X79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
@@ -7269,29 +7269,29 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -7313,7 +7313,7 @@
         <v>15</v>
       </c>
       <c r="K80" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -7321,10 +7321,10 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P80" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="X80" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y80" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
@@ -7344,29 +7344,29 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P81" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -7407,10 +7407,10 @@
         </is>
       </c>
       <c r="X81" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y81" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
@@ -7419,29 +7419,29 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -7463,7 +7463,7 @@
         <v>15</v>
       </c>
       <c r="K82" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="X82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
@@ -7494,29 +7494,29 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -7538,7 +7538,7 @@
         <v>15</v>
       </c>
       <c r="K83" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -7546,10 +7546,10 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P83" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -7576,22 +7576,22 @@
     <row r="84">
       <c r="B84" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7613,7 +7613,7 @@
         <v>15</v>
       </c>
       <c r="K84" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -7621,10 +7621,10 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P84" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -7651,22 +7651,22 @@
     <row r="85">
       <c r="B85" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -7688,7 +7688,7 @@
         <v>15</v>
       </c>
       <c r="K85" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P85" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="X85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
@@ -7726,22 +7726,22 @@
     <row r="86">
       <c r="B86" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -7763,7 +7763,7 @@
         <v>15</v>
       </c>
       <c r="K86" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -7771,10 +7771,10 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P86" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -7782,10 +7782,10 @@
         </is>
       </c>
       <c r="X86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
@@ -7801,22 +7801,22 @@
     <row r="87">
       <c r="B87" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -7846,10 +7846,10 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P87" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -7857,10 +7857,10 @@
         </is>
       </c>
       <c r="X87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
@@ -7876,22 +7876,22 @@
     <row r="88">
       <c r="B88" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P88" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="X88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
@@ -7951,22 +7951,22 @@
     <row r="89">
       <c r="B89" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7988,7 +7988,7 @@
         <v>15</v>
       </c>
       <c r="K89" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P89" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -8026,22 +8026,22 @@
     <row r="90">
       <c r="B90" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -8063,7 +8063,7 @@
         <v>15</v>
       </c>
       <c r="K90" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -8071,10 +8071,10 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P90" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -8101,22 +8101,22 @@
     <row r="91">
       <c r="B91" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -8138,7 +8138,7 @@
         <v>15</v>
       </c>
       <c r="K91" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -8146,10 +8146,10 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P91" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="X91" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y91" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
@@ -8176,22 +8176,22 @@
     <row r="92">
       <c r="B92" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -8213,7 +8213,7 @@
         <v>15</v>
       </c>
       <c r="K92" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P92" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -8232,10 +8232,10 @@
         </is>
       </c>
       <c r="X92" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y92" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
@@ -8251,22 +8251,22 @@
     <row r="93">
       <c r="B93" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -8288,7 +8288,7 @@
         <v>15</v>
       </c>
       <c r="K93" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -8296,10 +8296,10 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P93" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -8307,10 +8307,10 @@
         </is>
       </c>
       <c r="X93" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y93" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
@@ -8326,22 +8326,22 @@
     <row r="94">
       <c r="B94" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -8363,7 +8363,7 @@
         <v>15</v>
       </c>
       <c r="K94" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -8371,10 +8371,10 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P94" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="X94" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y94" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
@@ -8401,22 +8401,22 @@
     <row r="95">
       <c r="B95" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -8438,7 +8438,7 @@
         <v>15</v>
       </c>
       <c r="K95" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -8446,10 +8446,10 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P95" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -8476,22 +8476,22 @@
     <row r="96">
       <c r="B96" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -8513,7 +8513,7 @@
         <v>15</v>
       </c>
       <c r="K96" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P96" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -8551,22 +8551,22 @@
     <row r="97">
       <c r="B97" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -8596,10 +8596,10 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P97" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="X97" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y97" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
@@ -8626,22 +8626,22 @@
     <row r="98">
       <c r="B98" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P98" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -8682,10 +8682,10 @@
         </is>
       </c>
       <c r="X98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
@@ -8701,22 +8701,22 @@
     <row r="99">
       <c r="B99" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -8746,10 +8746,10 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P99" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -8757,10 +8757,10 @@
         </is>
       </c>
       <c r="X99" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y99" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
@@ -8776,22 +8776,22 @@
     <row r="100">
       <c r="B100" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P100" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -8832,10 +8832,10 @@
         </is>
       </c>
       <c r="X100" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y100" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
@@ -8851,22 +8851,22 @@
     <row r="101">
       <c r="B101" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -8888,7 +8888,7 @@
         <v>15</v>
       </c>
       <c r="K101" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P101" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="X101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
@@ -8926,22 +8926,22 @@
     <row r="102">
       <c r="B102" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -8963,7 +8963,7 @@
         <v>15</v>
       </c>
       <c r="K102" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -8971,10 +8971,10 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P102" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -8994,29 +8994,29 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -9038,7 +9038,7 @@
         <v>15</v>
       </c>
       <c r="K103" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -9057,10 +9057,10 @@
         </is>
       </c>
       <c r="X103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
@@ -9069,29 +9069,29 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -9113,7 +9113,7 @@
         <v>15</v>
       </c>
       <c r="K104" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P104" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -9132,10 +9132,10 @@
         </is>
       </c>
       <c r="X104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
@@ -9144,29 +9144,29 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="B105" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -9207,10 +9207,10 @@
         </is>
       </c>
       <c r="X105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
@@ -9219,29 +9219,29 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="B106" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P106" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -9282,10 +9282,10 @@
         </is>
       </c>
       <c r="X106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
@@ -9294,29 +9294,29 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="B107" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="X107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
@@ -9369,29 +9369,29 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -9413,7 +9413,7 @@
         <v>15</v>
       </c>
       <c r="K108" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -9421,10 +9421,10 @@
         </is>
       </c>
       <c r="O108" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P108" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -9444,29 +9444,29 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -9488,7 +9488,7 @@
         <v>15</v>
       </c>
       <c r="K109" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="X109" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y109" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
@@ -9519,29 +9519,29 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="B110" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -9563,7 +9563,7 @@
         <v>15</v>
       </c>
       <c r="K110" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -9571,10 +9571,10 @@
         </is>
       </c>
       <c r="O110" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P110" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="X110" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y110" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
@@ -9594,29 +9594,29 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="B111" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -9638,7 +9638,7 @@
         <v>15</v>
       </c>
       <c r="K111" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -9657,10 +9657,10 @@
         </is>
       </c>
       <c r="X111" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y111" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
@@ -9669,29 +9669,29 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="B112" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -9713,7 +9713,7 @@
         <v>15</v>
       </c>
       <c r="K112" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="O112" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P112" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -9732,10 +9732,10 @@
         </is>
       </c>
       <c r="X112" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y112" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z112" t="inlineStr">
         <is>
@@ -9744,29 +9744,29 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="X113" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y113" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z113" t="inlineStr">
         <is>
@@ -9819,29 +9819,29 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="B114" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -9863,7 +9863,7 @@
         <v>15</v>
       </c>
       <c r="K114" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -9871,10 +9871,10 @@
         </is>
       </c>
       <c r="O114" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P114" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -9894,29 +9894,29 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="B115" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -9938,7 +9938,7 @@
         <v>15</v>
       </c>
       <c r="K115" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -9957,10 +9957,10 @@
         </is>
       </c>
       <c r="X115" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y115" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
@@ -9969,29 +9969,29 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="B116" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -10021,10 +10021,10 @@
         </is>
       </c>
       <c r="O116" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P116" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="X116" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y116" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
@@ -10044,29 +10044,29 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="B117" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -10088,7 +10088,7 @@
         <v>15</v>
       </c>
       <c r="K117" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -10107,10 +10107,10 @@
         </is>
       </c>
       <c r="X117" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y117" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
@@ -10119,29 +10119,29 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="B118" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -10171,10 +10171,10 @@
         </is>
       </c>
       <c r="O118" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P118" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="X118" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y118" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
@@ -10194,29 +10194,29 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="B119" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -10257,10 +10257,10 @@
         </is>
       </c>
       <c r="X119" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y119" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
@@ -10269,29 +10269,29 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="B120" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -10313,7 +10313,7 @@
         <v>15</v>
       </c>
       <c r="K120" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -10321,10 +10321,10 @@
         </is>
       </c>
       <c r="O120" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P120" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -10332,10 +10332,10 @@
         </is>
       </c>
       <c r="X120" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y120" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
@@ -10344,29 +10344,29 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="B121" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -10388,7 +10388,7 @@
         <v>15</v>
       </c>
       <c r="K121" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -10407,10 +10407,10 @@
         </is>
       </c>
       <c r="X121" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y121" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z121" t="inlineStr">
         <is>
@@ -10426,22 +10426,22 @@
     <row r="122">
       <c r="B122" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -10463,7 +10463,7 @@
         <v>15</v>
       </c>
       <c r="K122" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -10482,10 +10482,10 @@
         </is>
       </c>
       <c r="X122" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y122" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
@@ -10501,22 +10501,22 @@
     <row r="123">
       <c r="B123" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -10557,10 +10557,10 @@
         </is>
       </c>
       <c r="X123" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y123" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
@@ -10576,22 +10576,22 @@
     <row r="124">
       <c r="B124" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -10632,10 +10632,10 @@
         </is>
       </c>
       <c r="X124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
@@ -10651,22 +10651,22 @@
     <row r="125">
       <c r="B125" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="X125" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y125" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
@@ -10726,22 +10726,22 @@
     <row r="126">
       <c r="B126" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -10782,10 +10782,10 @@
         </is>
       </c>
       <c r="X126" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y126" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z126" t="inlineStr">
         <is>
@@ -10801,22 +10801,22 @@
     <row r="127">
       <c r="B127" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -10838,7 +10838,7 @@
         <v>15</v>
       </c>
       <c r="K127" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -10857,10 +10857,10 @@
         </is>
       </c>
       <c r="X127" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y127" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
@@ -10876,22 +10876,22 @@
     <row r="128">
       <c r="B128" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -10913,7 +10913,7 @@
         <v>15</v>
       </c>
       <c r="K128" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -10932,10 +10932,10 @@
         </is>
       </c>
       <c r="X128" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y128" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
@@ -10951,22 +10951,22 @@
     <row r="129">
       <c r="B129" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -10988,7 +10988,7 @@
         <v>15</v>
       </c>
       <c r="K129" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -11007,10 +11007,10 @@
         </is>
       </c>
       <c r="X129" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y129" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
@@ -11026,22 +11026,22 @@
     <row r="130">
       <c r="B130" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -11063,7 +11063,7 @@
         <v>15</v>
       </c>
       <c r="K130" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -11082,10 +11082,10 @@
         </is>
       </c>
       <c r="X130" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y130" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
@@ -11101,22 +11101,22 @@
     <row r="131">
       <c r="B131" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -11157,10 +11157,10 @@
         </is>
       </c>
       <c r="X131" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y131" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
@@ -11176,22 +11176,22 @@
     <row r="132">
       <c r="B132" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -11232,10 +11232,10 @@
         </is>
       </c>
       <c r="X132" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y132" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
@@ -11251,22 +11251,22 @@
     <row r="133">
       <c r="B133" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -11288,7 +11288,7 @@
         <v>15</v>
       </c>
       <c r="K133" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -11307,10 +11307,10 @@
         </is>
       </c>
       <c r="X133" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y133" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
@@ -11326,22 +11326,22 @@
     <row r="134">
       <c r="B134" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -11363,7 +11363,7 @@
         <v>15</v>
       </c>
       <c r="K134" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -11382,10 +11382,10 @@
         </is>
       </c>
       <c r="X134" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y134" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z134" t="inlineStr">
         <is>
@@ -11401,22 +11401,22 @@
     <row r="135">
       <c r="B135" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -11438,7 +11438,7 @@
         <v>15</v>
       </c>
       <c r="K135" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -11457,10 +11457,10 @@
         </is>
       </c>
       <c r="X135" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y135" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
@@ -11476,22 +11476,22 @@
     <row r="136">
       <c r="B136" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -11513,7 +11513,7 @@
         <v>15</v>
       </c>
       <c r="K136" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -11532,10 +11532,10 @@
         </is>
       </c>
       <c r="X136" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y136" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
@@ -11551,22 +11551,22 @@
     <row r="137">
       <c r="B137" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -11607,10 +11607,10 @@
         </is>
       </c>
       <c r="X137" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y137" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z137" t="inlineStr">
         <is>
@@ -11626,22 +11626,22 @@
     <row r="138">
       <c r="B138" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -11682,10 +11682,10 @@
         </is>
       </c>
       <c r="X138" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y138" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
@@ -11701,22 +11701,22 @@
     <row r="139">
       <c r="B139" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -11738,7 +11738,7 @@
         <v>15</v>
       </c>
       <c r="K139" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -11746,10 +11746,10 @@
         </is>
       </c>
       <c r="O139" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P139" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -11776,22 +11776,22 @@
     <row r="140">
       <c r="B140" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -11813,7 +11813,7 @@
         <v>15</v>
       </c>
       <c r="K140" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -11832,10 +11832,10 @@
         </is>
       </c>
       <c r="X140" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y140" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
@@ -11844,29 +11844,29 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="B141" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -11888,7 +11888,7 @@
         <v>15</v>
       </c>
       <c r="K141" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -11896,10 +11896,10 @@
         </is>
       </c>
       <c r="O141" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P141" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
@@ -11907,10 +11907,10 @@
         </is>
       </c>
       <c r="X141" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y141" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
@@ -11919,29 +11919,29 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="B142" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -11982,10 +11982,10 @@
         </is>
       </c>
       <c r="X142" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y142" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
@@ -11994,29 +11994,29 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="B143" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -12046,10 +12046,10 @@
         </is>
       </c>
       <c r="O143" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P143" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
@@ -12057,10 +12057,10 @@
         </is>
       </c>
       <c r="X143" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y143" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z143" t="inlineStr">
         <is>
@@ -12069,29 +12069,29 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="B144" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -12132,10 +12132,10 @@
         </is>
       </c>
       <c r="X144" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y144" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
@@ -12144,29 +12144,29 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="B145" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -12188,7 +12188,7 @@
         <v>15</v>
       </c>
       <c r="K145" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -12196,10 +12196,10 @@
         </is>
       </c>
       <c r="O145" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P145" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -12207,10 +12207,10 @@
         </is>
       </c>
       <c r="X145" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y145" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z145" t="inlineStr">
         <is>
@@ -12219,29 +12219,29 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="B146" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -12263,7 +12263,7 @@
         <v>15</v>
       </c>
       <c r="K146" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -12282,10 +12282,10 @@
         </is>
       </c>
       <c r="X146" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y146" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
@@ -12294,29 +12294,29 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="B147" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -12338,7 +12338,7 @@
         <v>15</v>
       </c>
       <c r="K147" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -12346,10 +12346,10 @@
         </is>
       </c>
       <c r="O147" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P147" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -12357,10 +12357,10 @@
         </is>
       </c>
       <c r="X147" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y147" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z147" t="inlineStr">
         <is>
@@ -12369,29 +12369,29 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="B148" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -12413,7 +12413,7 @@
         <v>15</v>
       </c>
       <c r="K148" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -12432,10 +12432,10 @@
         </is>
       </c>
       <c r="X148" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y148" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
@@ -12444,29 +12444,29 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="B149" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -12496,10 +12496,10 @@
         </is>
       </c>
       <c r="O149" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P149" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -12507,10 +12507,10 @@
         </is>
       </c>
       <c r="X149" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y149" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
@@ -12519,29 +12519,29 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="B150" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -12582,10 +12582,10 @@
         </is>
       </c>
       <c r="X150" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y150" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
@@ -12594,29 +12594,29 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="B151" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -12638,7 +12638,7 @@
         <v>15</v>
       </c>
       <c r="K151" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -12646,10 +12646,10 @@
         </is>
       </c>
       <c r="O151" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P151" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
@@ -12657,10 +12657,10 @@
         </is>
       </c>
       <c r="X151" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y151" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
@@ -12669,29 +12669,29 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="B152" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -12713,7 +12713,7 @@
         <v>15</v>
       </c>
       <c r="K152" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -12732,10 +12732,10 @@
         </is>
       </c>
       <c r="X152" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y152" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
@@ -12744,29 +12744,29 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="B153" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -12788,7 +12788,7 @@
         <v>15</v>
       </c>
       <c r="K153" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -12796,10 +12796,10 @@
         </is>
       </c>
       <c r="O153" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P153" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
@@ -12807,10 +12807,10 @@
         </is>
       </c>
       <c r="X153" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y153" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
@@ -12819,29 +12819,29 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="B154" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -12863,7 +12863,7 @@
         <v>15</v>
       </c>
       <c r="K154" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="X154" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y154" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z154" t="inlineStr">
         <is>
@@ -12894,29 +12894,29 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="B155" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -12938,7 +12938,7 @@
         <v>15</v>
       </c>
       <c r="K155" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -12946,10 +12946,10 @@
         </is>
       </c>
       <c r="O155" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P155" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -12957,10 +12957,10 @@
         </is>
       </c>
       <c r="X155" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y155" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z155" t="inlineStr">
         <is>
@@ -12969,29 +12969,29 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="B156" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -13032,10 +13032,10 @@
         </is>
       </c>
       <c r="X156" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y156" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z156" t="inlineStr">
         <is>
@@ -13044,29 +13044,29 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="B157" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -13088,7 +13088,7 @@
         <v>15</v>
       </c>
       <c r="K157" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -13096,10 +13096,10 @@
         </is>
       </c>
       <c r="O157" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P157" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -13107,10 +13107,10 @@
         </is>
       </c>
       <c r="X157" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y157" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z157" t="inlineStr">
         <is>
@@ -13119,29 +13119,29 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="B158" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -13163,7 +13163,7 @@
         <v>15</v>
       </c>
       <c r="K158" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -13171,10 +13171,10 @@
         </is>
       </c>
       <c r="O158" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P158" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -13194,29 +13194,29 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="B159" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -13238,7 +13238,7 @@
         <v>15</v>
       </c>
       <c r="K159" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -13246,10 +13246,10 @@
         </is>
       </c>
       <c r="O159" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P159" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -13257,10 +13257,10 @@
         </is>
       </c>
       <c r="X159" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y159" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z159" t="inlineStr">
         <is>
@@ -13276,22 +13276,22 @@
     <row r="160">
       <c r="B160" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -13313,7 +13313,7 @@
         <v>15</v>
       </c>
       <c r="K160" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -13321,10 +13321,10 @@
         </is>
       </c>
       <c r="O160" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P160" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -13332,10 +13332,10 @@
         </is>
       </c>
       <c r="X160" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y160" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z160" t="inlineStr">
         <is>
@@ -13351,22 +13351,22 @@
     <row r="161">
       <c r="B161" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -13396,10 +13396,10 @@
         </is>
       </c>
       <c r="O161" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P161" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -13407,10 +13407,10 @@
         </is>
       </c>
       <c r="X161" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y161" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
@@ -13426,22 +13426,22 @@
     <row r="162">
       <c r="B162" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -13471,10 +13471,10 @@
         </is>
       </c>
       <c r="O162" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P162" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
@@ -13482,10 +13482,10 @@
         </is>
       </c>
       <c r="X162" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y162" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z162" t="inlineStr">
         <is>
@@ -13501,22 +13501,22 @@
     <row r="163">
       <c r="B163" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -13538,7 +13538,7 @@
         <v>15</v>
       </c>
       <c r="K163" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -13546,10 +13546,10 @@
         </is>
       </c>
       <c r="O163" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P163" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -13557,10 +13557,10 @@
         </is>
       </c>
       <c r="X163" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y163" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
@@ -13576,22 +13576,22 @@
     <row r="164">
       <c r="B164" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -13613,7 +13613,7 @@
         <v>15</v>
       </c>
       <c r="K164" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -13621,10 +13621,10 @@
         </is>
       </c>
       <c r="O164" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P164" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -13632,10 +13632,10 @@
         </is>
       </c>
       <c r="X164" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y164" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z164" t="inlineStr">
         <is>
@@ -13651,22 +13651,22 @@
     <row r="165">
       <c r="B165" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -13688,7 +13688,7 @@
         <v>15</v>
       </c>
       <c r="K165" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -13696,10 +13696,10 @@
         </is>
       </c>
       <c r="O165" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P165" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -13707,10 +13707,10 @@
         </is>
       </c>
       <c r="X165" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y165" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z165" t="inlineStr">
         <is>
@@ -13726,22 +13726,22 @@
     <row r="166">
       <c r="B166" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -13763,7 +13763,7 @@
         <v>15</v>
       </c>
       <c r="K166" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -13771,10 +13771,10 @@
         </is>
       </c>
       <c r="O166" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P166" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -13782,10 +13782,10 @@
         </is>
       </c>
       <c r="X166" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y166" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
@@ -13801,22 +13801,22 @@
     <row r="167">
       <c r="B167" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -13846,10 +13846,10 @@
         </is>
       </c>
       <c r="O167" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P167" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -13857,10 +13857,10 @@
         </is>
       </c>
       <c r="X167" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y167" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
@@ -13876,22 +13876,22 @@
     <row r="168">
       <c r="B168" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -13921,30 +13921,705 @@
         </is>
       </c>
       <c r="O168" t="n">
+        <v>100</v>
+      </c>
+      <c r="P168" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X168" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2246A09</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2246009</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>15</v>
+      </c>
+      <c r="K169" t="n">
+        <v>80</v>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O169" t="n">
         <v>110</v>
       </c>
-      <c r="P168" t="n">
+      <c r="P169" t="n">
         <v>110</v>
       </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X168" t="n">
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X169" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2246A09</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2246009</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>15</v>
+      </c>
+      <c r="K170" t="n">
+        <v>80</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O170" t="n">
+        <v>110</v>
+      </c>
+      <c r="P170" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X170" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2246A09</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2246009</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>15</v>
+      </c>
+      <c r="K171" t="n">
+        <v>69</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O171" t="n">
+        <v>90</v>
+      </c>
+      <c r="P171" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X171" t="n">
         <v>20</v>
       </c>
-      <c r="Y168" t="n">
+      <c r="Y171" t="n">
         <v>20</v>
       </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA168" t="inlineStr">
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2246A09</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2246009</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>15</v>
+      </c>
+      <c r="K172" t="n">
+        <v>69</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O172" t="n">
+        <v>90</v>
+      </c>
+      <c r="P172" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X172" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2246A09</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2246009</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>15</v>
+      </c>
+      <c r="K173" t="n">
+        <v>79</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O173" t="n">
+        <v>100</v>
+      </c>
+      <c r="P173" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X173" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2246A09</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2246009</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>15</v>
+      </c>
+      <c r="K174" t="n">
+        <v>79</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O174" t="n">
+        <v>100</v>
+      </c>
+      <c r="P174" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X174" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2246A09</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2246009</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>15</v>
+      </c>
+      <c r="K175" t="n">
+        <v>80</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O175" t="n">
+        <v>110</v>
+      </c>
+      <c r="P175" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X175" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2246A09</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2246009</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>15</v>
+      </c>
+      <c r="K176" t="n">
+        <v>80</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O176" t="n">
+        <v>110</v>
+      </c>
+      <c r="P176" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X176" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2246A09</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2246009</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>15</v>
+      </c>
+      <c r="K177" t="n">
+        <v>79</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O177" t="n">
+        <v>100</v>
+      </c>
+      <c r="P177" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X177" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/output/upload/S00026_2246_H건강플러스보험_무배당.xlsx
+++ b/output/upload/S00026_2246_H건강플러스보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV177"/>
+  <dimension ref="A1:AV168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -1339,12 +1339,16 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n"/>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J7" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
@@ -1371,10 +1375,10 @@
       <c r="V7" s="6" t="n"/>
       <c r="W7" s="6" t="n"/>
       <c r="X7" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y7" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z7" s="6" t="inlineStr">
         <is>
@@ -1445,12 +1449,16 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J8" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
@@ -1477,10 +1485,10 @@
       <c r="V8" s="6" t="n"/>
       <c r="W8" s="6" t="n"/>
       <c r="X8" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y8" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z8" s="6" t="inlineStr">
         <is>
@@ -1551,12 +1559,16 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n"/>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J9" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
@@ -1566,10 +1578,10 @@
       <c r="M9" s="6" t="n"/>
       <c r="N9" s="6" t="n"/>
       <c r="O9" s="6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
@@ -1583,10 +1595,10 @@
       <c r="V9" s="6" t="n"/>
       <c r="W9" s="6" t="n"/>
       <c r="X9" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y9" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z9" s="6" t="inlineStr">
         <is>
@@ -1657,12 +1669,16 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I10" s="6" t="n"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J10" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
@@ -1672,10 +1688,10 @@
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n"/>
       <c r="O10" s="6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
@@ -1689,10 +1705,10 @@
       <c r="V10" s="6" t="n"/>
       <c r="W10" s="6" t="n"/>
       <c r="X10" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y10" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z10" s="6" t="inlineStr">
         <is>
@@ -1763,12 +1779,16 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I11" s="6" t="n"/>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J11" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
@@ -1778,10 +1798,10 @@
       <c r="M11" s="6" t="n"/>
       <c r="N11" s="6" t="n"/>
       <c r="O11" s="6" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q11" s="6" t="inlineStr">
         <is>
@@ -1869,12 +1889,16 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I12" s="6" t="n"/>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J12" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
@@ -1884,10 +1908,10 @@
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n"/>
       <c r="O12" s="6" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
@@ -1975,12 +1999,16 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I13" s="6" t="n"/>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J13" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
@@ -1990,10 +2018,10 @@
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
       <c r="O13" s="6" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
@@ -2081,12 +2109,16 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I14" s="6" t="n"/>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J14" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
@@ -2096,10 +2128,10 @@
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
       <c r="O14" s="6" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
@@ -2113,10 +2145,10 @@
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
       <c r="X14" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y14" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z14" s="6" t="inlineStr">
         <is>
@@ -2125,7 +2157,7 @@
       </c>
       <c r="AA14" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB14" s="6" t="n"/>
@@ -2187,12 +2219,16 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I15" s="6" t="n"/>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J15" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
@@ -2219,10 +2255,10 @@
       <c r="V15" s="6" t="n"/>
       <c r="W15" s="6" t="n"/>
       <c r="X15" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y15" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z15" s="6" t="inlineStr">
         <is>
@@ -2231,7 +2267,7 @@
       </c>
       <c r="AA15" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="6" t="n"/>
@@ -2293,7 +2329,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I16" s="6" t="n"/>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J16" s="6" t="n">
         <v>15</v>
       </c>
@@ -2325,10 +2365,10 @@
       <c r="V16" s="6" t="n"/>
       <c r="W16" s="6" t="n"/>
       <c r="X16" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y16" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z16" s="6" t="inlineStr">
         <is>
@@ -2337,7 +2377,7 @@
       </c>
       <c r="AA16" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB16" s="6" t="n"/>
@@ -2399,7 +2439,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I17" s="6" t="n"/>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J17" s="6" t="n">
         <v>15</v>
       </c>
@@ -2414,10 +2458,10 @@
       <c r="M17" s="6" t="n"/>
       <c r="N17" s="6" t="n"/>
       <c r="O17" s="6" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q17" s="6" t="inlineStr">
         <is>
@@ -2431,10 +2475,10 @@
       <c r="V17" s="6" t="n"/>
       <c r="W17" s="6" t="n"/>
       <c r="X17" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y17" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z17" s="6" t="inlineStr">
         <is>
@@ -2443,7 +2487,7 @@
       </c>
       <c r="AA17" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="6" t="n"/>
@@ -2505,7 +2549,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I18" s="6" t="n"/>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J18" s="6" t="n">
         <v>15</v>
       </c>
@@ -2537,10 +2585,10 @@
       <c r="V18" s="6" t="n"/>
       <c r="W18" s="6" t="n"/>
       <c r="X18" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y18" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z18" s="6" t="inlineStr">
         <is>
@@ -2549,7 +2597,7 @@
       </c>
       <c r="AA18" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB18" s="6" t="n"/>
@@ -2611,12 +2659,16 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I19" s="6" t="n"/>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J19" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
@@ -2626,10 +2678,10 @@
       <c r="M19" s="6" t="n"/>
       <c r="N19" s="6" t="n"/>
       <c r="O19" s="6" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
@@ -2643,10 +2695,10 @@
       <c r="V19" s="6" t="n"/>
       <c r="W19" s="6" t="n"/>
       <c r="X19" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y19" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z19" s="6" t="inlineStr">
         <is>
@@ -2655,7 +2707,7 @@
       </c>
       <c r="AA19" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="6" t="n"/>
@@ -2717,12 +2769,16 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I20" s="6" t="n"/>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J20" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
@@ -2732,10 +2788,10 @@
       <c r="M20" s="6" t="n"/>
       <c r="N20" s="6" t="n"/>
       <c r="O20" s="6" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
@@ -2749,10 +2805,10 @@
       <c r="V20" s="6" t="n"/>
       <c r="W20" s="6" t="n"/>
       <c r="X20" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y20" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z20" s="6" t="inlineStr">
         <is>
@@ -2823,12 +2879,16 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I21" s="6" t="n"/>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J21" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
@@ -2838,10 +2898,10 @@
       <c r="M21" s="6" t="n"/>
       <c r="N21" s="6" t="n"/>
       <c r="O21" s="6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
@@ -2855,10 +2915,10 @@
       <c r="V21" s="6" t="n"/>
       <c r="W21" s="6" t="n"/>
       <c r="X21" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y21" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z21" s="6" t="inlineStr">
         <is>
@@ -2929,12 +2989,16 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I22" s="6" t="n"/>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J22" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
@@ -2944,10 +3008,10 @@
       <c r="M22" s="6" t="n"/>
       <c r="N22" s="6" t="n"/>
       <c r="O22" s="6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
@@ -2961,10 +3025,10 @@
       <c r="V22" s="6" t="n"/>
       <c r="W22" s="6" t="n"/>
       <c r="X22" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y22" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z22" s="6" t="inlineStr">
         <is>
@@ -3034,6 +3098,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J23" t="n">
         <v>15</v>
       </c>
@@ -3109,6 +3178,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J24" t="n">
         <v>15</v>
       </c>
@@ -3151,22 +3225,22 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3184,11 +3258,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J25" t="n">
         <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -3196,10 +3275,10 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P25" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3207,10 +3286,10 @@
         </is>
       </c>
       <c r="X25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3259,11 +3338,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J26" t="n">
         <v>15</v>
       </c>
       <c r="K26" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3282,10 +3366,10 @@
         </is>
       </c>
       <c r="X26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -3294,7 +3378,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -3334,11 +3418,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J27" t="n">
         <v>15</v>
       </c>
       <c r="K27" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -3357,10 +3446,10 @@
         </is>
       </c>
       <c r="X27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -3369,7 +3458,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3409,11 +3498,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J28" t="n">
         <v>15</v>
       </c>
       <c r="K28" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -3421,10 +3515,10 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P28" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -3432,10 +3526,10 @@
         </is>
       </c>
       <c r="X28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3444,7 +3538,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -3484,11 +3578,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J29" t="n">
         <v>15</v>
       </c>
       <c r="K29" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3496,10 +3595,10 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P29" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -3519,7 +3618,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3559,11 +3658,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J30" t="n">
         <v>15</v>
       </c>
       <c r="K30" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -3571,10 +3675,10 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P30" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -3594,7 +3698,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -3634,11 +3738,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J31" t="n">
         <v>15</v>
       </c>
       <c r="K31" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -3646,10 +3755,10 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P31" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -3657,10 +3766,10 @@
         </is>
       </c>
       <c r="X31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -3669,7 +3778,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3709,11 +3818,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J32" t="n">
         <v>15</v>
       </c>
       <c r="K32" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3721,10 +3835,10 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P32" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -3732,10 +3846,10 @@
         </is>
       </c>
       <c r="X32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
@@ -3744,7 +3858,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -3784,11 +3898,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J33" t="n">
         <v>15</v>
       </c>
       <c r="K33" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -3796,10 +3915,10 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -3807,10 +3926,10 @@
         </is>
       </c>
       <c r="X33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -3819,7 +3938,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3859,6 +3978,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J34" t="n">
         <v>15</v>
       </c>
@@ -3882,10 +4006,10 @@
         </is>
       </c>
       <c r="X34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
@@ -3894,7 +4018,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -3934,6 +4058,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J35" t="n">
         <v>15</v>
       </c>
@@ -3946,10 +4075,10 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P35" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -3957,10 +4086,10 @@
         </is>
       </c>
       <c r="X35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -3969,7 +4098,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4009,6 +4138,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J36" t="n">
         <v>15</v>
       </c>
@@ -4032,10 +4166,10 @@
         </is>
       </c>
       <c r="X36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -4044,7 +4178,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -4084,6 +4218,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J37" t="n">
         <v>15</v>
       </c>
@@ -4096,10 +4235,10 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P37" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -4119,7 +4258,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4159,11 +4298,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J38" t="n">
         <v>15</v>
       </c>
       <c r="K38" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4171,10 +4315,10 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -4182,10 +4326,10 @@
         </is>
       </c>
       <c r="X38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -4194,7 +4338,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -4234,11 +4378,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J39" t="n">
         <v>15</v>
       </c>
       <c r="K39" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -4246,10 +4395,10 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P39" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -4257,10 +4406,10 @@
         </is>
       </c>
       <c r="X39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -4269,7 +4418,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4309,11 +4458,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J40" t="n">
         <v>15</v>
       </c>
       <c r="K40" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -4321,10 +4475,10 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P40" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -4332,10 +4486,10 @@
         </is>
       </c>
       <c r="X40" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y40" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -4344,7 +4498,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -4384,11 +4538,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J41" t="n">
         <v>15</v>
       </c>
       <c r="K41" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -4396,10 +4555,10 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P41" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -4419,7 +4578,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4459,6 +4618,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J42" t="n">
         <v>15</v>
       </c>
@@ -4494,29 +4658,29 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>2246A02</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2246002</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4534,11 +4698,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J43" t="n">
         <v>15</v>
       </c>
       <c r="K43" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -4546,10 +4715,10 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P43" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -4569,29 +4738,29 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>2246A02</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2246002</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4609,11 +4778,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J44" t="n">
         <v>15</v>
       </c>
       <c r="K44" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -4621,10 +4795,10 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P44" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -4632,10 +4806,10 @@
         </is>
       </c>
       <c r="X44" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y44" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -4644,7 +4818,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -4684,11 +4858,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J45" t="n">
         <v>15</v>
       </c>
       <c r="K45" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -4707,10 +4886,10 @@
         </is>
       </c>
       <c r="X45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -4759,11 +4938,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J46" t="n">
         <v>15</v>
       </c>
       <c r="K46" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -4782,10 +4966,10 @@
         </is>
       </c>
       <c r="X46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -4834,11 +5018,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J47" t="n">
         <v>15</v>
       </c>
       <c r="K47" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -4846,10 +5035,10 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P47" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -4909,11 +5098,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J48" t="n">
         <v>15</v>
       </c>
       <c r="K48" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -4921,10 +5115,10 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P48" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -4984,11 +5178,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J49" t="n">
         <v>15</v>
       </c>
       <c r="K49" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -4996,10 +5195,10 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P49" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -5007,10 +5206,10 @@
         </is>
       </c>
       <c r="X49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
@@ -5059,11 +5258,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J50" t="n">
         <v>15</v>
       </c>
       <c r="K50" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -5071,10 +5275,10 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -5082,10 +5286,10 @@
         </is>
       </c>
       <c r="X50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
@@ -5134,11 +5338,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J51" t="n">
         <v>15</v>
       </c>
       <c r="K51" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -5146,10 +5355,10 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P51" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -5157,10 +5366,10 @@
         </is>
       </c>
       <c r="X51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
@@ -5209,11 +5418,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J52" t="n">
         <v>15</v>
       </c>
       <c r="K52" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -5221,10 +5435,10 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -5232,10 +5446,10 @@
         </is>
       </c>
       <c r="X52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
@@ -5284,6 +5498,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J53" t="n">
         <v>15</v>
       </c>
@@ -5296,10 +5515,10 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P53" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -5307,10 +5526,10 @@
         </is>
       </c>
       <c r="X53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
@@ -5359,6 +5578,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J54" t="n">
         <v>15</v>
       </c>
@@ -5371,10 +5595,10 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P54" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -5382,10 +5606,10 @@
         </is>
       </c>
       <c r="X54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
@@ -5434,6 +5658,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J55" t="n">
         <v>15</v>
       </c>
@@ -5446,10 +5675,10 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -5509,6 +5738,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J56" t="n">
         <v>15</v>
       </c>
@@ -5521,10 +5755,10 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P56" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -5584,11 +5818,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J57" t="n">
         <v>15</v>
       </c>
       <c r="K57" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -5596,10 +5835,10 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P57" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -5607,10 +5846,10 @@
         </is>
       </c>
       <c r="X57" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y57" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
@@ -5659,11 +5898,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J58" t="n">
         <v>15</v>
       </c>
       <c r="K58" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -5671,10 +5915,10 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P58" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -5682,10 +5926,10 @@
         </is>
       </c>
       <c r="X58" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y58" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
@@ -5734,11 +5978,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J59" t="n">
         <v>15</v>
       </c>
       <c r="K59" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -5746,10 +5995,10 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P59" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -5809,11 +6058,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J60" t="n">
         <v>15</v>
       </c>
       <c r="K60" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -5821,10 +6075,10 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P60" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -5851,22 +6105,22 @@
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>2246A03</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2246003</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5884,11 +6138,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J61" t="n">
         <v>15</v>
       </c>
       <c r="K61" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -5896,10 +6155,10 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P61" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -5926,22 +6185,22 @@
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t>2246A03</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2246003</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5959,11 +6218,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J62" t="n">
         <v>15</v>
       </c>
       <c r="K62" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -5971,10 +6235,10 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P62" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -6001,22 +6265,22 @@
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>2246A03</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2246003</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6034,11 +6298,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J63" t="n">
         <v>15</v>
       </c>
       <c r="K63" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -6046,10 +6315,10 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P63" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -6109,11 +6378,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J64" t="n">
         <v>15</v>
       </c>
       <c r="K64" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -6132,10 +6406,10 @@
         </is>
       </c>
       <c r="X64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
@@ -6144,7 +6418,7 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6184,6 +6458,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J65" t="n">
         <v>15</v>
       </c>
@@ -6219,7 +6498,7 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6259,11 +6538,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J66" t="n">
         <v>15</v>
       </c>
       <c r="K66" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -6271,10 +6555,10 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P66" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -6294,7 +6578,7 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6334,11 +6618,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J67" t="n">
         <v>15</v>
       </c>
       <c r="K67" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -6357,10 +6646,10 @@
         </is>
       </c>
       <c r="X67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
@@ -6369,7 +6658,7 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6409,11 +6698,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J68" t="n">
         <v>15</v>
       </c>
       <c r="K68" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -6421,10 +6715,10 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P68" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -6432,10 +6726,10 @@
         </is>
       </c>
       <c r="X68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
@@ -6444,7 +6738,7 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6484,6 +6778,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J69" t="n">
         <v>15</v>
       </c>
@@ -6496,10 +6795,10 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P69" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -6519,7 +6818,7 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6559,11 +6858,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J70" t="n">
         <v>15</v>
       </c>
       <c r="K70" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -6571,10 +6875,10 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P70" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -6582,10 +6886,10 @@
         </is>
       </c>
       <c r="X70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
@@ -6594,7 +6898,7 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6634,11 +6938,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J71" t="n">
         <v>15</v>
       </c>
       <c r="K71" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -6646,10 +6955,10 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P71" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -6657,10 +6966,10 @@
         </is>
       </c>
       <c r="X71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
@@ -6669,7 +6978,7 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6709,6 +7018,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J72" t="n">
         <v>15</v>
       </c>
@@ -6721,10 +7035,10 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P72" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -6732,10 +7046,10 @@
         </is>
       </c>
       <c r="X72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
@@ -6744,7 +7058,7 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6784,6 +7098,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J73" t="n">
         <v>15</v>
       </c>
@@ -6819,7 +7138,7 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6859,6 +7178,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J74" t="n">
         <v>15</v>
       </c>
@@ -6871,10 +7195,10 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P74" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -6894,7 +7218,7 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6934,6 +7258,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J75" t="n">
         <v>15</v>
       </c>
@@ -6969,7 +7298,7 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7009,11 +7338,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J76" t="n">
         <v>15</v>
       </c>
       <c r="K76" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -7021,10 +7355,10 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P76" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -7032,10 +7366,10 @@
         </is>
       </c>
       <c r="X76" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y76" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
@@ -7044,7 +7378,7 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -7084,11 +7418,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J77" t="n">
         <v>15</v>
       </c>
       <c r="K77" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -7096,10 +7435,10 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P77" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -7119,7 +7458,7 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7159,11 +7498,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J78" t="n">
         <v>15</v>
       </c>
       <c r="K78" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -7171,10 +7515,10 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P78" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -7194,29 +7538,29 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="inlineStr">
         <is>
-          <t>2246A04</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2246004</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -7234,11 +7578,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J79" t="n">
         <v>15</v>
       </c>
       <c r="K79" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -7246,10 +7595,10 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P79" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -7269,29 +7618,29 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="inlineStr">
         <is>
-          <t>2246A04</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2246004</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -7309,11 +7658,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J80" t="n">
         <v>15</v>
       </c>
       <c r="K80" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -7321,10 +7675,10 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P80" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -7344,29 +7698,29 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="inlineStr">
         <is>
-          <t>2246A04</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2246004</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -7384,11 +7738,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J81" t="n">
         <v>15</v>
       </c>
       <c r="K81" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -7396,10 +7755,10 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P81" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -7407,10 +7766,10 @@
         </is>
       </c>
       <c r="X81" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y81" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
@@ -7419,29 +7778,29 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="inlineStr">
         <is>
-          <t>2246A04</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2246004</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -7459,11 +7818,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J82" t="n">
         <v>15</v>
       </c>
       <c r="K82" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -7471,10 +7835,10 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P82" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -7494,7 +7858,7 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -7534,6 +7898,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J83" t="n">
         <v>15</v>
       </c>
@@ -7609,6 +7978,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J84" t="n">
         <v>15</v>
       </c>
@@ -7684,11 +8058,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J85" t="n">
         <v>15</v>
       </c>
       <c r="K85" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -7707,10 +8086,10 @@
         </is>
       </c>
       <c r="X85" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y85" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
@@ -7759,11 +8138,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J86" t="n">
         <v>15</v>
       </c>
       <c r="K86" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -7782,10 +8166,10 @@
         </is>
       </c>
       <c r="X86" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y86" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
@@ -7834,6 +8218,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J87" t="n">
         <v>15</v>
       </c>
@@ -7846,10 +8235,10 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P87" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -7909,6 +8298,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J88" t="n">
         <v>15</v>
       </c>
@@ -7921,10 +8315,10 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P88" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -7984,11 +8378,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J89" t="n">
         <v>15</v>
       </c>
       <c r="K89" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -7996,10 +8395,10 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P89" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -8007,10 +8406,10 @@
         </is>
       </c>
       <c r="X89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
@@ -8059,11 +8458,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J90" t="n">
         <v>15</v>
       </c>
       <c r="K90" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -8071,10 +8475,10 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P90" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -8082,10 +8486,10 @@
         </is>
       </c>
       <c r="X90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
@@ -8134,6 +8538,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J91" t="n">
         <v>15</v>
       </c>
@@ -8209,6 +8618,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J92" t="n">
         <v>15</v>
       </c>
@@ -8284,6 +8698,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J93" t="n">
         <v>15</v>
       </c>
@@ -8359,6 +8778,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J94" t="n">
         <v>15</v>
       </c>
@@ -8434,11 +8858,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J95" t="n">
         <v>15</v>
       </c>
       <c r="K95" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -8446,10 +8875,10 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P95" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -8509,11 +8938,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J96" t="n">
         <v>15</v>
       </c>
       <c r="K96" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -8521,10 +8955,10 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P96" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -8551,22 +8985,22 @@
     <row r="97">
       <c r="B97" t="inlineStr">
         <is>
-          <t>2246A05</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2246005</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -8584,11 +9018,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J97" t="n">
         <v>15</v>
       </c>
       <c r="K97" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -8596,10 +9035,10 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P97" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -8626,22 +9065,22 @@
     <row r="98">
       <c r="B98" t="inlineStr">
         <is>
-          <t>2246A05</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2246005</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -8659,11 +9098,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J98" t="n">
         <v>15</v>
       </c>
       <c r="K98" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -8671,10 +9115,10 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P98" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -8701,22 +9145,22 @@
     <row r="99">
       <c r="B99" t="inlineStr">
         <is>
-          <t>2246A05</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2246005</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -8734,11 +9178,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J99" t="n">
         <v>15</v>
       </c>
       <c r="K99" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -8746,10 +9195,10 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P99" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -8757,10 +9206,10 @@
         </is>
       </c>
       <c r="X99" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y99" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
@@ -8776,22 +9225,22 @@
     <row r="100">
       <c r="B100" t="inlineStr">
         <is>
-          <t>2246A05</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2246005</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8809,11 +9258,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J100" t="n">
         <v>15</v>
       </c>
       <c r="K100" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -8821,10 +9275,10 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P100" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -8832,10 +9286,10 @@
         </is>
       </c>
       <c r="X100" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y100" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
@@ -8851,22 +9305,22 @@
     <row r="101">
       <c r="B101" t="inlineStr">
         <is>
-          <t>2246A05</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2246005</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -8882,6 +9336,11 @@
       <c r="H101" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -8896,10 +9355,10 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P101" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -8907,10 +9366,10 @@
         </is>
       </c>
       <c r="X101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
@@ -8959,6 +9418,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J102" t="n">
         <v>15</v>
       </c>
@@ -8994,7 +9458,7 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -9034,6 +9498,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J103" t="n">
         <v>15</v>
       </c>
@@ -9046,10 +9515,10 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P103" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -9057,10 +9526,10 @@
         </is>
       </c>
       <c r="X103" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y103" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
@@ -9069,7 +9538,7 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9109,11 +9578,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J104" t="n">
         <v>15</v>
       </c>
       <c r="K104" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -9132,10 +9606,10 @@
         </is>
       </c>
       <c r="X104" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y104" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
@@ -9144,7 +9618,7 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -9184,6 +9658,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J105" t="n">
         <v>15</v>
       </c>
@@ -9219,7 +9698,7 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9259,6 +9738,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J106" t="n">
         <v>15</v>
       </c>
@@ -9271,10 +9755,10 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P106" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -9294,7 +9778,7 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -9334,6 +9818,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J107" t="n">
         <v>15</v>
       </c>
@@ -9369,7 +9858,7 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9409,11 +9898,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J108" t="n">
         <v>15</v>
       </c>
       <c r="K108" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -9421,10 +9915,10 @@
         </is>
       </c>
       <c r="O108" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P108" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -9432,10 +9926,10 @@
         </is>
       </c>
       <c r="X108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
@@ -9444,7 +9938,7 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -9484,11 +9978,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J109" t="n">
         <v>15</v>
       </c>
       <c r="K109" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -9496,10 +9995,10 @@
         </is>
       </c>
       <c r="O109" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P109" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -9519,7 +10018,7 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9559,6 +10058,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J110" t="n">
         <v>15</v>
       </c>
@@ -9594,7 +10098,7 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -9634,6 +10138,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J111" t="n">
         <v>15</v>
       </c>
@@ -9646,10 +10155,10 @@
         </is>
       </c>
       <c r="O111" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P111" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -9669,7 +10178,7 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9709,6 +10218,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J112" t="n">
         <v>15</v>
       </c>
@@ -9744,7 +10258,7 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -9784,6 +10298,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J113" t="n">
         <v>15</v>
       </c>
@@ -9807,10 +10326,10 @@
         </is>
       </c>
       <c r="X113" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y113" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z113" t="inlineStr">
         <is>
@@ -9819,7 +10338,7 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9859,11 +10378,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J114" t="n">
         <v>15</v>
       </c>
       <c r="K114" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -9871,10 +10395,10 @@
         </is>
       </c>
       <c r="O114" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P114" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -9894,29 +10418,29 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="B115" t="inlineStr">
         <is>
-          <t>2246A06</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2246006</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -9932,6 +10456,11 @@
       <c r="H115" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -9969,29 +10498,29 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="B116" t="inlineStr">
         <is>
-          <t>2246A06</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2246006</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -10009,11 +10538,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J116" t="n">
         <v>15</v>
       </c>
       <c r="K116" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -10021,10 +10555,10 @@
         </is>
       </c>
       <c r="O116" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P116" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -10044,29 +10578,29 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="B117" t="inlineStr">
         <is>
-          <t>2246A06</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2246006</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -10084,11 +10618,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J117" t="n">
         <v>15</v>
       </c>
       <c r="K117" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -10096,10 +10635,10 @@
         </is>
       </c>
       <c r="O117" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P117" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -10107,10 +10646,10 @@
         </is>
       </c>
       <c r="X117" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y117" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
@@ -10119,29 +10658,29 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="B118" t="inlineStr">
         <is>
-          <t>2246A06</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2246006</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -10159,11 +10698,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J118" t="n">
         <v>15</v>
       </c>
       <c r="K118" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -10171,10 +10715,10 @@
         </is>
       </c>
       <c r="O118" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P118" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -10182,10 +10726,10 @@
         </is>
       </c>
       <c r="X118" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y118" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
@@ -10194,29 +10738,29 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="B119" t="inlineStr">
         <is>
-          <t>2246A06</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2246006</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -10234,11 +10778,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J119" t="n">
         <v>15</v>
       </c>
       <c r="K119" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -10246,10 +10795,10 @@
         </is>
       </c>
       <c r="O119" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P119" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -10257,10 +10806,10 @@
         </is>
       </c>
       <c r="X119" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y119" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
@@ -10269,29 +10818,29 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="B120" t="inlineStr">
         <is>
-          <t>2246A06</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2246006</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -10307,6 +10856,11 @@
       <c r="H120" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -10321,10 +10875,10 @@
         </is>
       </c>
       <c r="O120" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P120" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -10332,10 +10886,10 @@
         </is>
       </c>
       <c r="X120" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y120" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
@@ -10344,7 +10898,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -10384,6 +10938,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J121" t="n">
         <v>15</v>
       </c>
@@ -10396,10 +10955,10 @@
         </is>
       </c>
       <c r="O121" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P121" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -10407,10 +10966,10 @@
         </is>
       </c>
       <c r="X121" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y121" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z121" t="inlineStr">
         <is>
@@ -10459,6 +11018,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J122" t="n">
         <v>15</v>
       </c>
@@ -10471,10 +11035,10 @@
         </is>
       </c>
       <c r="O122" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P122" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -10482,10 +11046,10 @@
         </is>
       </c>
       <c r="X122" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y122" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
@@ -10534,6 +11098,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J123" t="n">
         <v>15</v>
       </c>
@@ -10609,6 +11178,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J124" t="n">
         <v>15</v>
       </c>
@@ -10684,6 +11258,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J125" t="n">
         <v>15</v>
       </c>
@@ -10759,6 +11338,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J126" t="n">
         <v>15</v>
       </c>
@@ -10834,11 +11418,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J127" t="n">
         <v>15</v>
       </c>
       <c r="K127" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -10846,10 +11435,10 @@
         </is>
       </c>
       <c r="O127" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P127" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -10909,11 +11498,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J128" t="n">
         <v>15</v>
       </c>
       <c r="K128" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -10921,10 +11515,10 @@
         </is>
       </c>
       <c r="O128" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P128" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -10984,6 +11578,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J129" t="n">
         <v>15</v>
       </c>
@@ -10996,10 +11595,10 @@
         </is>
       </c>
       <c r="O129" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P129" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -11059,6 +11658,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J130" t="n">
         <v>15</v>
       </c>
@@ -11071,10 +11675,10 @@
         </is>
       </c>
       <c r="O130" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P130" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -11134,6 +11738,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J131" t="n">
         <v>15</v>
       </c>
@@ -11157,10 +11766,10 @@
         </is>
       </c>
       <c r="X131" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y131" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
@@ -11209,6 +11818,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J132" t="n">
         <v>15</v>
       </c>
@@ -11232,10 +11846,10 @@
         </is>
       </c>
       <c r="X132" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y132" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
@@ -11251,22 +11865,22 @@
     <row r="133">
       <c r="B133" t="inlineStr">
         <is>
-          <t>2246A07</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2246007</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -11282,6 +11896,11 @@
       <c r="H133" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -11326,22 +11945,22 @@
     <row r="134">
       <c r="B134" t="inlineStr">
         <is>
-          <t>2246A07</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2246007</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -11357,6 +11976,11 @@
       <c r="H134" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -11401,22 +12025,22 @@
     <row r="135">
       <c r="B135" t="inlineStr">
         <is>
-          <t>2246A07</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2246007</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -11434,11 +12058,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J135" t="n">
         <v>15</v>
       </c>
       <c r="K135" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -11446,10 +12075,10 @@
         </is>
       </c>
       <c r="O135" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P135" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -11457,10 +12086,10 @@
         </is>
       </c>
       <c r="X135" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y135" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
@@ -11476,22 +12105,22 @@
     <row r="136">
       <c r="B136" t="inlineStr">
         <is>
-          <t>2246A07</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2246007</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -11509,11 +12138,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J136" t="n">
         <v>15</v>
       </c>
       <c r="K136" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -11521,10 +12155,10 @@
         </is>
       </c>
       <c r="O136" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P136" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -11532,10 +12166,10 @@
         </is>
       </c>
       <c r="X136" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y136" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
@@ -11551,22 +12185,22 @@
     <row r="137">
       <c r="B137" t="inlineStr">
         <is>
-          <t>2246A07</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2246007</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -11584,11 +12218,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J137" t="n">
         <v>15</v>
       </c>
       <c r="K137" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -11596,10 +12235,10 @@
         </is>
       </c>
       <c r="O137" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P137" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -11607,10 +12246,10 @@
         </is>
       </c>
       <c r="X137" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y137" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z137" t="inlineStr">
         <is>
@@ -11626,22 +12265,22 @@
     <row r="138">
       <c r="B138" t="inlineStr">
         <is>
-          <t>2246A07</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2246007</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -11659,11 +12298,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J138" t="n">
         <v>15</v>
       </c>
       <c r="K138" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -11671,10 +12315,10 @@
         </is>
       </c>
       <c r="O138" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P138" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -11682,10 +12326,10 @@
         </is>
       </c>
       <c r="X138" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y138" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
@@ -11701,22 +12345,22 @@
     <row r="139">
       <c r="B139" t="inlineStr">
         <is>
-          <t>2246A07</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2246007</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -11732,6 +12376,11 @@
       <c r="H139" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -11757,10 +12406,10 @@
         </is>
       </c>
       <c r="X139" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y139" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
@@ -11809,6 +12458,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J140" t="n">
         <v>15</v>
       </c>
@@ -11821,10 +12475,10 @@
         </is>
       </c>
       <c r="O140" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P140" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -11832,10 +12486,10 @@
         </is>
       </c>
       <c r="X140" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y140" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
@@ -11844,7 +12498,7 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -11884,11 +12538,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J141" t="n">
         <v>15</v>
       </c>
       <c r="K141" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -11896,10 +12555,10 @@
         </is>
       </c>
       <c r="O141" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P141" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
@@ -11919,7 +12578,7 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -11959,6 +12618,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J142" t="n">
         <v>15</v>
       </c>
@@ -11994,7 +12658,7 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -12034,6 +12698,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J143" t="n">
         <v>15</v>
       </c>
@@ -12046,10 +12715,10 @@
         </is>
       </c>
       <c r="O143" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P143" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
@@ -12069,7 +12738,7 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -12109,6 +12778,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J144" t="n">
         <v>15</v>
       </c>
@@ -12144,7 +12818,7 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -12184,6 +12858,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J145" t="n">
         <v>15</v>
       </c>
@@ -12196,10 +12875,10 @@
         </is>
       </c>
       <c r="O145" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P145" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -12207,10 +12886,10 @@
         </is>
       </c>
       <c r="X145" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y145" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z145" t="inlineStr">
         <is>
@@ -12219,7 +12898,7 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -12259,11 +12938,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J146" t="n">
         <v>15</v>
       </c>
       <c r="K146" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -12271,10 +12955,10 @@
         </is>
       </c>
       <c r="O146" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P146" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
@@ -12294,7 +12978,7 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -12334,11 +13018,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J147" t="n">
         <v>15</v>
       </c>
       <c r="K147" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -12346,10 +13035,10 @@
         </is>
       </c>
       <c r="O147" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P147" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -12369,7 +13058,7 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -12409,6 +13098,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J148" t="n">
         <v>15</v>
       </c>
@@ -12421,10 +13115,10 @@
         </is>
       </c>
       <c r="O148" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P148" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -12444,7 +13138,7 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -12484,6 +13178,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J149" t="n">
         <v>15</v>
       </c>
@@ -12496,10 +13195,10 @@
         </is>
       </c>
       <c r="O149" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P149" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -12507,10 +13206,10 @@
         </is>
       </c>
       <c r="X149" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y149" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
@@ -12519,7 +13218,7 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -12559,6 +13258,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J150" t="n">
         <v>15</v>
       </c>
@@ -12582,10 +13286,10 @@
         </is>
       </c>
       <c r="X150" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y150" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
@@ -12594,29 +13298,29 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="B151" t="inlineStr">
         <is>
-          <t>2246A08</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2246008</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -12634,11 +13338,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J151" t="n">
         <v>15</v>
       </c>
       <c r="K151" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -12646,10 +13355,10 @@
         </is>
       </c>
       <c r="O151" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P151" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
@@ -12657,10 +13366,10 @@
         </is>
       </c>
       <c r="X151" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y151" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
@@ -12669,29 +13378,29 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="B152" t="inlineStr">
         <is>
-          <t>2246A08</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2246008</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -12707,6 +13416,11 @@
       <c r="H152" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -12744,29 +13458,29 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="B153" t="inlineStr">
         <is>
-          <t>2246A08</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2246008</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -12784,11 +13498,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J153" t="n">
         <v>15</v>
       </c>
       <c r="K153" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -12807,10 +13526,10 @@
         </is>
       </c>
       <c r="X153" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y153" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
@@ -12819,29 +13538,29 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="B154" t="inlineStr">
         <is>
-          <t>2246A08</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2246008</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -12859,11 +13578,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J154" t="n">
         <v>15</v>
       </c>
       <c r="K154" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -12871,10 +13595,10 @@
         </is>
       </c>
       <c r="O154" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P154" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -12882,10 +13606,10 @@
         </is>
       </c>
       <c r="X154" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y154" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z154" t="inlineStr">
         <is>
@@ -12894,29 +13618,29 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="B155" t="inlineStr">
         <is>
-          <t>2246A08</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2246008</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -12932,6 +13656,11 @@
       <c r="H155" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J155" t="n">
@@ -12946,10 +13675,10 @@
         </is>
       </c>
       <c r="O155" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P155" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -12957,10 +13686,10 @@
         </is>
       </c>
       <c r="X155" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y155" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z155" t="inlineStr">
         <is>
@@ -12969,29 +13698,29 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="B156" t="inlineStr">
         <is>
-          <t>2246A08</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2246008</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -13009,11 +13738,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J156" t="n">
         <v>15</v>
       </c>
       <c r="K156" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -13021,10 +13755,10 @@
         </is>
       </c>
       <c r="O156" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P156" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -13032,10 +13766,10 @@
         </is>
       </c>
       <c r="X156" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y156" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z156" t="inlineStr">
         <is>
@@ -13044,29 +13778,29 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="B157" t="inlineStr">
         <is>
-          <t>2246A08</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2246008</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -13084,11 +13818,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J157" t="n">
         <v>15</v>
       </c>
       <c r="K157" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -13096,10 +13835,10 @@
         </is>
       </c>
       <c r="O157" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P157" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -13119,29 +13858,29 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="B158" t="inlineStr">
         <is>
-          <t>2246A08</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2246008</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -13157,6 +13896,11 @@
       <c r="H158" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -13182,10 +13926,10 @@
         </is>
       </c>
       <c r="X158" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y158" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z158" t="inlineStr">
         <is>
@@ -13194,7 +13938,7 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -13234,11 +13978,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J159" t="n">
         <v>15</v>
       </c>
       <c r="K159" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -13246,10 +13995,10 @@
         </is>
       </c>
       <c r="O159" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P159" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -13309,11 +14058,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J160" t="n">
         <v>15</v>
       </c>
       <c r="K160" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -13321,10 +14075,10 @@
         </is>
       </c>
       <c r="O160" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P160" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -13384,6 +14138,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J161" t="n">
         <v>15</v>
       </c>
@@ -13396,10 +14155,10 @@
         </is>
       </c>
       <c r="O161" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P161" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -13459,6 +14218,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J162" t="n">
         <v>15</v>
       </c>
@@ -13471,10 +14235,10 @@
         </is>
       </c>
       <c r="O162" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P162" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
@@ -13534,6 +14298,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J163" t="n">
         <v>15</v>
       </c>
@@ -13546,10 +14315,10 @@
         </is>
       </c>
       <c r="O163" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P163" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -13557,10 +14326,10 @@
         </is>
       </c>
       <c r="X163" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y163" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
@@ -13609,6 +14378,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J164" t="n">
         <v>15</v>
       </c>
@@ -13621,10 +14395,10 @@
         </is>
       </c>
       <c r="O164" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P164" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -13632,10 +14406,10 @@
         </is>
       </c>
       <c r="X164" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y164" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z164" t="inlineStr">
         <is>
@@ -13684,11 +14458,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J165" t="n">
         <v>15</v>
       </c>
       <c r="K165" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -13696,10 +14475,10 @@
         </is>
       </c>
       <c r="O165" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P165" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -13759,11 +14538,16 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J166" t="n">
         <v>15</v>
       </c>
       <c r="K166" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -13771,10 +14555,10 @@
         </is>
       </c>
       <c r="O166" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P166" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -13834,6 +14618,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J167" t="n">
         <v>15</v>
       </c>
@@ -13846,10 +14635,10 @@
         </is>
       </c>
       <c r="O167" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P167" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -13857,10 +14646,10 @@
         </is>
       </c>
       <c r="X167" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y167" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
@@ -13909,6 +14698,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J168" t="n">
         <v>15</v>
       </c>
@@ -13921,10 +14715,10 @@
         </is>
       </c>
       <c r="O168" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P168" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
@@ -13932,10 +14726,10 @@
         </is>
       </c>
       <c r="X168" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y168" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
@@ -13945,681 +14739,6 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>2246A09</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>2246009</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J169" t="n">
-        <v>15</v>
-      </c>
-      <c r="K169" t="n">
-        <v>80</v>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O169" t="n">
-        <v>110</v>
-      </c>
-      <c r="P169" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X169" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y169" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA169" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>2246A09</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>2246009</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J170" t="n">
-        <v>15</v>
-      </c>
-      <c r="K170" t="n">
-        <v>80</v>
-      </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O170" t="n">
-        <v>110</v>
-      </c>
-      <c r="P170" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q170" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X170" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y170" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>2246A09</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>2246009</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J171" t="n">
-        <v>15</v>
-      </c>
-      <c r="K171" t="n">
-        <v>69</v>
-      </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O171" t="n">
-        <v>90</v>
-      </c>
-      <c r="P171" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X171" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y171" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>2246A09</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>2246009</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J172" t="n">
-        <v>15</v>
-      </c>
-      <c r="K172" t="n">
-        <v>69</v>
-      </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O172" t="n">
-        <v>90</v>
-      </c>
-      <c r="P172" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X172" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y172" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA172" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>2246A09</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>2246009</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J173" t="n">
-        <v>15</v>
-      </c>
-      <c r="K173" t="n">
-        <v>79</v>
-      </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O173" t="n">
-        <v>100</v>
-      </c>
-      <c r="P173" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X173" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y173" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA173" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>2246A09</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>2246009</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J174" t="n">
-        <v>15</v>
-      </c>
-      <c r="K174" t="n">
-        <v>79</v>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O174" t="n">
-        <v>100</v>
-      </c>
-      <c r="P174" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X174" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y174" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA174" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>2246A09</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>2246009</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J175" t="n">
-        <v>15</v>
-      </c>
-      <c r="K175" t="n">
-        <v>80</v>
-      </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O175" t="n">
-        <v>110</v>
-      </c>
-      <c r="P175" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X175" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y175" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>2246A09</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>2246009</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J176" t="n">
-        <v>15</v>
-      </c>
-      <c r="K176" t="n">
-        <v>80</v>
-      </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O176" t="n">
-        <v>110</v>
-      </c>
-      <c r="P176" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X176" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y176" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA176" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>2246A09</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>2246009</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J177" t="n">
-        <v>15</v>
-      </c>
-      <c r="K177" t="n">
-        <v>79</v>
-      </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O177" t="n">
-        <v>100</v>
-      </c>
-      <c r="P177" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X177" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y177" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
